--- a/CNT_Jira_Files/Zephyr Update/PF26_BFA1509R0.260603.1/iPhone.xlsx
+++ b/CNT_Jira_Files/Zephyr Update/PF26_BFA1509R0.260603.1/iPhone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chandrakanb\chandrakanb\CNT_Jira_Files\Zephyr Update\PF26_BFA1509R0.260603.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB740A1-719E-45F1-A5A1-12992504F3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76925F64-AE53-453B-8E28-EB6A1FBE6E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{37910DB9-48F5-49F3-9284-ABCB3482D904}"/>
   </bookViews>
@@ -143,22 +143,23 @@
     <t>3DAP1</t>
   </si>
   <si>
+    <t>[CNT][KPIT_TC_CNT_WCP_054][CarPlay]</t>
+  </si>
+  <si>
     <t>kpt_ghadge_va</t>
   </si>
   <si>
-    <t>[CNT][KPIT_TC_CNT_WCP_054][CarPlay]</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
     <t>CNT_Bench02</t>
   </si>
   <si>
-    <t>Fail | 3 |After step 3,"Apple CarPlay has stopped "(com.honda.ivi.carplay) crash popup is observed | PJ12DEF00-11015</t>
-  </si>
-  <si>
     <t>CNTKPIT-T13</t>
+  </si>
+  <si>
+    <t>Fail | 3 |After step 3,
+"Apple CarPlay has stopped "(com.honda.ivi.carplay) crash popup is observed | PJ12DEF00-11015</t>
   </si>
 </sst>
 </file>
@@ -218,8 +219,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,198 +567,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>32</v>
       </c>
     </row>
